--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.183428</v>
+        <v>0.390944</v>
       </c>
       <c r="D4" t="n">
-        <v>0.14222</v>
+        <v>0.209572</v>
       </c>
       <c r="E4" t="n">
-        <v>0.321817</v>
+        <v>0.790548</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.303457</v>
+        <v>0.603789</v>
       </c>
       <c r="D5" t="n">
-        <v>0.153026</v>
+        <v>0.306148</v>
       </c>
       <c r="E5" t="n">
-        <v>0.465255</v>
+        <v>0.944528</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.563588</v>
+        <v>0.766636</v>
       </c>
       <c r="D2" t="n">
-        <v>0.334179</v>
+        <v>0.476308</v>
       </c>
       <c r="E2" t="n">
-        <v>0.770825</v>
+        <v>0.91018</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.717422</v>
+        <v>0.864212</v>
       </c>
       <c r="D3" t="n">
-        <v>0.439594</v>
+        <v>0.648749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.826489</v>
+        <v>1.111115</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>500</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.390944</v>
+        <v>0.402157</v>
       </c>
       <c r="D4" t="n">
-        <v>0.209572</v>
+        <v>0.266831</v>
       </c>
       <c r="E4" t="n">
-        <v>0.790548</v>
+        <v>0.662677</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>500</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.603789</v>
+        <v>0.644163</v>
       </c>
       <c r="D5" t="n">
-        <v>0.306148</v>
+        <v>0.349041</v>
       </c>
       <c r="E5" t="n">
-        <v>0.944528</v>
+        <v>1.057987</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>500</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.402157</v>
+        <v>0.366969</v>
       </c>
       <c r="D4" t="n">
-        <v>0.266831</v>
+        <v>0.263217</v>
       </c>
       <c r="E4" t="n">
-        <v>0.662677</v>
+        <v>0.6627189999999999</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.644163</v>
+        <v>0.645267</v>
       </c>
       <c r="D5" t="n">
-        <v>0.349041</v>
+        <v>0.337009</v>
       </c>
       <c r="E5" t="n">
-        <v>1.057987</v>
+        <v>1.004442</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.766636</v>
+        <v>0.766024</v>
       </c>
       <c r="D2" t="n">
         <v>0.476308</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.864212</v>
+        <v>0.865683</v>
       </c>
       <c r="D3" t="n">
-        <v>0.648749</v>
+        <v>0.63929</v>
       </c>
       <c r="E3" t="n">
-        <v>1.111115</v>
+        <v>1.126038</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.366969</v>
+        <v>0.366637</v>
       </c>
       <c r="D4" t="n">
-        <v>0.263217</v>
+        <v>0.266865</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6627189999999999</v>
+        <v>0.6492250000000001</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645267</v>
+        <v>0.570881</v>
       </c>
       <c r="D5" t="n">
-        <v>0.337009</v>
+        <v>0.339694</v>
       </c>
       <c r="E5" t="n">
-        <v>1.004442</v>
+        <v>0.995848</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.366637</v>
+        <v>0.366273</v>
       </c>
       <c r="D4" t="n">
-        <v>0.266865</v>
+        <v>0.2666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6492250000000001</v>
+        <v>0.649878</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.570881</v>
+        <v>0.571163</v>
       </c>
       <c r="D5" t="n">
-        <v>0.339694</v>
+        <v>0.339805</v>
       </c>
       <c r="E5" t="n">
-        <v>0.995848</v>
+        <v>0.996833</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
